--- a/соответствие_категорий_ТЛТ.xlsx
+++ b/соответствие_категорий_ТЛТ.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -659,6 +659,18 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Мини-печи (настольные духовки)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Духовки настольные</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/соответствие_категорий_ТЛТ.xlsx
+++ b/соответствие_категорий_ТЛТ.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -671,6 +671,174 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Медная труба</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Дренаж</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Изоляция для трубы</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Крепеж (дюбеля, болты, гайки)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Кронштейны</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Лента тефлоновая,скотч</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Провод, вилки</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Фреон, MAPP Gas</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>(исключить)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Стабилизаторы напряжения 80-260В</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Стабилизаторы напряжения</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Стабилизаторы напряжения 100-260В</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Стабилизаторы напряжения</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Стандартные генераторы</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Генераторы</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Мотоблоки, двигатели, культиваторы, мотобуры, компрессоры</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Мотоблоки и садовая техника</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Холодильники капельные, Defrost</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Холодильники с верхней морозильной камерой</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Телевизоры, медиплееры, кронштейны</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Телевизоры 27"- 32"</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
